--- a/business_forms/006_e_commerce_audit_form--business_forms.xlsx
+++ b/business_forms/006_e_commerce_audit_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>e_commerce_audit_form</t>
+          <t>business_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>e_commerce_audit_form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the name of your business?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your business name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>business_category</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What category does your business fall under?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Choose one of the following options</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is your current website address?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter your website URL</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +601,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>category_2</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is your current social media presence?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Choose all that apply</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,64 +628,76 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>customer_satisfaction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is your current customer satisfaction rating?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>category_3</t>
+          <t>sales_volume</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is your current sales volume?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please enter a numerical value</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_ids_2</t>
+          <t>inventory_management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>form_ids_2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is your current inventory management system?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Choose one of the following options</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,41 +709,49 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>shipping_policy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is your current shipping policy?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please enter a brief description</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>payment_processing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is your current payment processing system?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Choose one of the following options</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +763,49 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>description_2</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is your current customer service process?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please enter a brief description</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t>marketing_strategy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your current marketing strategy?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Choose one of the following options</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_ids_3</t>
+          <t>goals_objectives</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>form_ids_3</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What are your current goals and objectives?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please enter a brief description</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +844,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>assigned_tool_2</t>
+          <t>target_audience</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>assigned_tool_2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What is your target audience?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please enter a brief description</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,271 +871,76 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>description_3</t>
+          <t>product_line</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What is your current product line?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please enter a brief description</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>output_file_2</t>
+          <t>pricing_strategy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>output_file_2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>What is your current pricing strategy?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Choose one of the following options</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>description_4</t>
+          <t>shipping_frequency</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>What is your current shipping frequency?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Choose one of the following options</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>assigned_tool_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>assigned_tool_3</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>description_5</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_ids_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>description_6</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>assigned_tool_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>description_7</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>description_8</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_ids_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>description_9</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +955,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,289 +983,612 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>business_category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>retail</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>business_category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>online_store</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>online store</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>business_category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>e-commerce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>e-commerce</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>business_category_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>wholesale</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>wholesale</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>business_category_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_2_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_2_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_2_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>category_2_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>category_3_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>category_3_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>category_3_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>pinterest</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Pinterest</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>category_3_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>categories_choices</t>
+          <t>inventory_management_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>categories_choices</t>
+          <t>inventory_management_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>automated</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>automated</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>categories_choices</t>
+          <t>inventory_management_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>hybrid</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>categories_choices</t>
+          <t>inventory_management_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>payment_processing_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>payment_processing_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>payment_processing_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>payment_processing_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>marketing_strategy_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>social media</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>marketing_strategy_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>email_marketing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>email marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>marketing_strategy_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>content_marketing</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>content marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>marketing_strategy_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>influencer_marketing</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>influencer marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>marketing_strategy_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>pricing_strategy_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>pricing_strategy_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>pricing_strategy_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>volume-based</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>volume-based</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pricing_strategy_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>tiered</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>tiered</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>pricing_strategy_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>shipping_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>shipping_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>shipping_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>shipping_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>shipping_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
